--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanBG_260826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanBG_260826.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\01. Báo giá sửa chữa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D8F3F2-E7D9-4804-AB77-E8CB9F9BF81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F7CD97-1321-480E-A821-C65BA5AFB2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$22</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -116,12 +116,6 @@
     <t>eSIM lỗi</t>
   </si>
   <si>
-    <t>eSIM</t>
-  </si>
-  <si>
-    <t>Phí dịch vụ hoà mạng</t>
-  </si>
-  <si>
     <t>007785070543254</t>
   </si>
   <si>
@@ -131,7 +125,10 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Báo giá chưa có phản hồi, đẩy qua tháng 09/2026</t>
+    <t>Khay Nano SIM</t>
+  </si>
+  <si>
+    <t>Báo giá khách đã đồng ý sủa chữa, công nợ ghi KD. Lực</t>
   </si>
 </sst>
 </file>
@@ -243,7 +240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -396,24 +393,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -495,19 +479,91 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -518,84 +574,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -956,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
@@ -978,82 +956,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39"/>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="45" t="s">
+      <c r="A1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="47"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="48" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="51" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="47"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="54" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="56"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="59"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="12"/>
@@ -1064,11 +1042,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -1078,11 +1056,11 @@
       <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23" t="s">
@@ -1095,11 +1073,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
@@ -1142,7 +1120,7 @@
         <v>19</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA10" s="2"/>
     </row>
@@ -1153,8 +1131,8 @@
       <c r="B11" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>33</v>
+      <c r="C11" s="30" t="s">
+        <v>31</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>23</v>
@@ -1163,7 +1141,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>24</v>
@@ -1174,167 +1152,155 @@
       <c r="I11" s="22">
         <v>50000</v>
       </c>
-      <c r="J11" s="31">
-        <f>SUM((H11*I11)+(H12*I12))</f>
-        <v>110000</v>
+      <c r="J11" s="29">
+        <f>SUM(H11*I11)</f>
+        <v>50000</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
+      <c r="A12" s="28">
+        <v>2</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>29</v>
+      </c>
       <c r="F12" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="29"/>
+        <v>33</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="H12" s="20">
         <v>1</v>
       </c>
       <c r="I12" s="22">
-        <v>60000</v>
-      </c>
-      <c r="J12" s="32"/>
+        <v>50000</v>
+      </c>
+      <c r="J12" s="29">
+        <f>SUM(H12*I12)</f>
+        <v>50000</v>
+      </c>
       <c r="K12" s="27"/>
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
-        <v>2</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="20">
-        <v>1</v>
-      </c>
-      <c r="I13" s="22">
-        <v>50000</v>
-      </c>
-      <c r="J13" s="31">
-        <f>SUM((H13*I13)+(H14*I14))</f>
-        <v>110000</v>
+      <c r="A13" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="19">
+        <f>SUM(J11:J12)</f>
+        <v>100000</v>
       </c>
       <c r="K13" s="27"/>
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="20">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="15"/>
+      <c r="AA14" s="2"/>
+    </row>
+    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="AA15" s="2"/>
+    </row>
+    <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="AA16" s="2"/>
+    </row>
+    <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="I14" s="22">
-        <v>60000</v>
-      </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="27"/>
-      <c r="AA14" s="2"/>
-    </row>
-    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="19">
-        <f>SUM(J11:J14)</f>
-        <v>220000</v>
-      </c>
-      <c r="K15" s="27"/>
-      <c r="AA15" s="2"/>
-    </row>
-    <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="15"/>
-      <c r="AA16" s="2"/>
-    </row>
-    <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="AA17" s="2"/>
-    </row>
-    <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1343,9 +1309,7 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="7" t="s">
-        <v>1</v>
-      </c>
+      <c r="F20" s="7"/>
       <c r="G20" s="13"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -1353,64 +1317,44 @@
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
+      <c r="A21" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="9"/>
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="9"/>
+    <row r="23" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F23" s="4"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="F25" s="4"/>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="AA25" s="2"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
@@ -1461,19 +1405,16 @@
     <row r="41" spans="27:27" x14ac:dyDescent="0.25">
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="27:27" x14ac:dyDescent="0.25">
-      <c r="AA42" s="2"/>
-    </row>
-    <row r="43" spans="27:27" x14ac:dyDescent="0.25">
-      <c r="AA43" s="2"/>
-    </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="31">
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A23:D23"/>
+  <mergeCells count="17">
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A1:D4"/>
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="E2:J2"/>
@@ -1484,23 +1425,6 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="G17:J17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
